--- a/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -553,13 +553,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―|㳞</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -594,13 +594,13 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―|㳞</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -853,13 +853,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳|―|㳞</t>
+          <t xml:space="preserve">湳|–|㳞</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―
+–
 㳞</t>
         </is>
       </c>
@@ -939,13 +939,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕|―|㳞</t>
+          <t xml:space="preserve">潕|–|㳞</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潕
-―
+–
 㳞</t>
         </is>
       </c>
@@ -1023,14 +1023,14 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑|―</t>
+          <t xml:space="preserve">無|姑|–</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㑖|㑖|―</t>
+          <t xml:space="preserve">㑖|㑖|–</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㑖
 㑖
-―</t>
+–</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1113,14 +1113,14 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|南|―</t>
+          <t xml:space="preserve">南|南|–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1511,13 +1511,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―|仲</t>
+          <t xml:space="preserve">姑|–|仲</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 仲</t>
         </is>
       </c>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㳞</t>
+          <t xml:space="preserve">–|㳞</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -1596,13 +1596,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|㳞</t>
+          <t xml:space="preserve">仲|–|㳞</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 㳞</t>
         </is>
       </c>
@@ -1677,13 +1677,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―|仲</t>
+          <t xml:space="preserve">汰|–|仲</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 仲</t>
         </is>
       </c>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㳞</t>
+          <t xml:space="preserve">–|㳞</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -1762,14 +1762,14 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|仲|―</t>
+          <t xml:space="preserve">無|仲|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1846,13 +1846,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―|仲</t>
+          <t xml:space="preserve">㳞|–|仲</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 仲</t>
         </is>
       </c>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㳞</t>
+          <t xml:space="preserve">–|㳞</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|㳞|―</t>
+          <t xml:space="preserve">汰|㳞|–</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -2178,13 +2178,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―|仲</t>
+          <t xml:space="preserve">姑|–|仲</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 仲</t>
         </is>
       </c>
@@ -2260,13 +2260,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|㳞</t>
+          <t xml:space="preserve">仲|–|㳞</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 㳞</t>
         </is>
       </c>
@@ -2384,13 +2384,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2831,14 +2831,14 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|㳞|―</t>
+          <t xml:space="preserve">仲|㳞|–</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2872,14 +2872,14 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|㳞|―</t>
+          <t xml:space="preserve">仲|㳞|–</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2913,13 +2913,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|㳞</t>
+          <t xml:space="preserve">仲|–|㳞</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 㳞</t>
         </is>
       </c>
@@ -2997,13 +2997,13 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3085,13 +3085,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|潢</t>
+          <t xml:space="preserve">無|–|潢</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 潢</t>
         </is>
       </c>
@@ -3331,13 +3331,13 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|仲</t>
+          <t xml:space="preserve">潢|–|仲</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 仲</t>
         </is>
       </c>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -3839,13 +3839,13 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―|㳞</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -3880,13 +3880,13 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―|㳞</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -3921,13 +3921,13 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―|㳞</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4001,13 +4001,13 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳|―|㳞</t>
+          <t xml:space="preserve">湳|–|㳞</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4087,13 +4087,13 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳|―|㳞</t>
+          <t xml:space="preserve">湳|–|㳞</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4175,14 +4175,14 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑|―</t>
+          <t xml:space="preserve">姑|姑|–</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -4220,14 +4220,14 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|仲|―</t>
+          <t xml:space="preserve">仲|仲|–</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4569,7 +4569,7 @@
       <c r="H3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 仲</t>
         </is>
       </c>
@@ -4592,7 +4592,7 @@
       <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4607,7 +4607,7 @@
       <c r="B4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="H4" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -4665,7 +4665,7 @@
       <c r="L4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4680,7 +4680,7 @@
       <c r="B5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4715,7 +4715,7 @@
         <is>
           <t xml:space="preserve">汰
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
@@ -4816,7 +4816,7 @@
       <c r="B7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4828,7 +4828,7 @@
       <c r="D7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 仲</t>
         </is>
       </c>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -4944,7 +4944,7 @@
       <c r="B9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―
+–
 㳞</t>
         </is>
       </c>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5064,7 +5064,7 @@
         <is>
           <t xml:space="preserve">姑
 姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -5087,7 +5087,7 @@
         <is>
           <t xml:space="preserve">仲
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -5098,7 +5098,7 @@
       <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 仲</t>
         </is>
       </c>
@@ -5110,7 +5110,7 @@
       <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 仲</t>
         </is>
       </c>
@@ -5122,7 +5122,7 @@
       <c r="L11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―
+–
 㳞</t>
         </is>
       </c>
@@ -5138,7 +5138,7 @@
         <is>
           <t xml:space="preserve">仲
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -5161,7 +5161,7 @@
         <is>
           <t xml:space="preserve">仲
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -5232,7 +5232,7 @@
       <c r="F13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 㳞</t>
         </is>
       </c>
@@ -5244,7 +5244,7 @@
       <c r="H13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 㳞</t>
         </is>
       </c>
@@ -5256,7 +5256,7 @@
       <c r="J13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 㳞</t>
         </is>
       </c>
@@ -5268,7 +5268,7 @@
       <c r="L13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潕
-―
+–
 㳞</t>
         </is>
       </c>
@@ -5371,7 +5371,7 @@
       <c r="F15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -5393,7 +5393,7 @@
       <c r="J15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 仲</t>
         </is>
       </c>
@@ -5406,7 +5406,7 @@
         <is>
           <t xml:space="preserve">無
 姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -5454,7 +5454,7 @@
       <c r="H16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -5477,7 +5477,7 @@
         <is>
           <t xml:space="preserve">㑖
 㑖
-―</t>
+–</t>
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr">
@@ -5514,7 +5514,7 @@
       <c r="F17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 潢</t>
         </is>
       </c>
@@ -5539,7 +5539,7 @@
         <is>
           <t xml:space="preserve">無
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -5551,7 +5551,7 @@
         <is>
           <t xml:space="preserve">南
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">

--- a/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4512,91 +4553,91 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –
 㳞</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">방</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –
 仲</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">붉은</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –
 㳞</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
@@ -4604,72 +4645,72 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –
 㳞</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">긋</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南
 仲</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南
 仲</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –
 㳞</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4677,70 +4718,70 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –
 㳞</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">시요</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">방</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 仲</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㳞
 –</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">파란</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 姑</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -4748,64 +4789,64 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃사</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">긋</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">홍의</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃이</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -4813,320 +4854,320 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 –
 㳞</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 仲</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">방</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃이</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M7" s="8"/>
+      <c r="M7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
 㳞</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
 㳞</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">긋</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M8" s="9"/>
+      <c r="M8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 –
 㳞</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사요</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">웃는</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">코도</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M9" s="9"/>
+      <c r="M9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃을사</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">하얀꽃</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="27"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M10" s="10"/>
+      <c r="M10" s="27"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑
 –</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">활</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞
 –</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풀을</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –
 仲</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –
 仲</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 –
 㳞</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
@@ -5134,72 +5175,72 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
 –</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">짝</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞
 –</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">뜯어</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
 㳞</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">색잔</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr">
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">바구</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
 㳞</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -5207,72 +5248,72 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">피었</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 㳞</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">메고</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 㳞</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">치의</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 㳞</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">니들</t>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潕
 –
 㳞</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사시</t>
         </is>
@@ -5280,64 +5321,64 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">러메</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -5345,71 +5386,71 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –
 仲</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="K15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">고꽃</t>
         </is>
       </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 –</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃을</t>
         </is>
@@ -5417,70 +5458,70 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 仲</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 南</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">피</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">빛</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">팔</t>
         </is>
       </c>
-      <c r="L16" s="18" t="inlineStr">
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㑖
 㑖
 –</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr">
+      <c r="M16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5488,73 +5529,73 @@
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 仲</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃을</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –
 潢</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">모진</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南
 南</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">울긋</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲
 –</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">러나</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南
 –</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑사</t>
         </is>
@@ -5562,62 +5603,62 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">뽀얀</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">불긋</t>
         </is>
       </c>
-      <c r="J18" s="18" t="inlineStr">
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K18" s="13" t="inlineStr">
+      <c r="K18" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">왔소</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>

--- a/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
@@ -4534,24 +4534,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="25" t="inlineStr">
@@ -4787,11 +4787,11 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M6" s="27" t="inlineStr">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K8" s="25" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
@@ -1478,12 +1478,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K9" s="25" t="inlineStr">

--- a/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
@@ -2829,12 +2829,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G10" s="28" t="inlineStr">

--- a/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (꽃은 모리).xlsx
@@ -4616,7 +4616,8 @@
       </c>
       <c r="I3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">붉은</t>
+          <t xml:space="preserve">붉
+은</t>
         </is>
       </c>
       <c r="J3" s="23" t="inlineStr">
@@ -4727,7 +4728,8 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">시요</t>
+          <t xml:space="preserve">시
+요</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -4761,7 +4763,8 @@
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">파란</t>
+          <t xml:space="preserve">파
+란</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -4796,7 +4799,8 @@
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃사</t>
+          <t xml:space="preserve">꽃
+사</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -4817,7 +4821,8 @@
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">홍의</t>
+          <t xml:space="preserve">홍
+의</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -4838,7 +4843,8 @@
       </c>
       <c r="K6" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃이</t>
+          <t xml:space="preserve">꽃
+이</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -4885,7 +4891,8 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃이</t>
+          <t xml:space="preserve">꽃
+이</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -4991,7 +4998,8 @@
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">사요</t>
+          <t xml:space="preserve">사
+요</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -5002,7 +5010,8 @@
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">웃는</t>
+          <t xml:space="preserve">웃
+는</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -5023,7 +5032,8 @@
       </c>
       <c r="I9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">코도</t>
+          <t xml:space="preserve">코
+도</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -5052,7 +5062,9 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃을사</t>
+          <t xml:space="preserve">꽃
+을
+사</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -5083,7 +5095,9 @@
       </c>
       <c r="I10" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">하얀꽃</t>
+          <t xml:space="preserve">하
+얀
+꽃</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -5133,7 +5147,8 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">풀을</t>
+          <t xml:space="preserve">풀
+을</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -5207,7 +5222,8 @@
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">뜯어</t>
+          <t xml:space="preserve">뜯
+어</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -5219,7 +5235,8 @@
       </c>
       <c r="I12" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">색잔</t>
+          <t xml:space="preserve">색
+잔</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -5230,7 +5247,8 @@
       </c>
       <c r="K12" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">바구</t>
+          <t xml:space="preserve">바
+구</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -5267,7 +5285,8 @@
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">피었</t>
+          <t xml:space="preserve">피
+었</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -5279,7 +5298,8 @@
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">메고</t>
+          <t xml:space="preserve">메
+고</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -5291,7 +5311,8 @@
       </c>
       <c r="I13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">치의</t>
+          <t xml:space="preserve">치
+의</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -5303,7 +5324,8 @@
       </c>
       <c r="K13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">니들</t>
+          <t xml:space="preserve">니
+들</t>
         </is>
       </c>
       <c r="L13" s="23" t="inlineStr">
@@ -5315,7 +5337,8 @@
       </c>
       <c r="M13" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">사시</t>
+          <t xml:space="preserve">사
+시</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5393,8 @@
       </c>
       <c r="K14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">러메</t>
+          <t xml:space="preserve">러
+메</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -5440,7 +5464,8 @@
       </c>
       <c r="K15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">고꽃</t>
+          <t xml:space="preserve">고
+꽃</t>
         </is>
       </c>
       <c r="L15" s="23" t="inlineStr">
@@ -5452,7 +5477,8 @@
       </c>
       <c r="M15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃을</t>
+          <t xml:space="preserve">꽃
+을</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5575,8 @@
       </c>
       <c r="E17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃을</t>
+          <t xml:space="preserve">꽃
+을</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -5561,7 +5588,8 @@
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">모진</t>
+          <t xml:space="preserve">모
+진</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -5573,7 +5601,8 @@
       </c>
       <c r="I17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">울긋</t>
+          <t xml:space="preserve">울
+긋</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -5585,7 +5614,8 @@
       </c>
       <c r="K17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">러나</t>
+          <t xml:space="preserve">러
+나</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -5597,7 +5627,8 @@
       </c>
       <c r="M17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑사</t>
+          <t xml:space="preserve">랑
+사</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5651,8 @@
       </c>
       <c r="E18" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">뽀얀</t>
+          <t xml:space="preserve">뽀
+얀</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -5640,7 +5672,8 @@
       </c>
       <c r="I18" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">불긋</t>
+          <t xml:space="preserve">불
+긋</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
@@ -5650,7 +5683,8 @@
       </c>
       <c r="K18" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">왔소</t>
+          <t xml:space="preserve">왔
+소</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
